--- a/projects/auto_page/autopageMKII/tables/Accel_mode13-10-2026.xlsx
+++ b/projects/auto_page/autopageMKII/tables/Accel_mode13-10-2026.xlsx
@@ -1064,7 +1064,7 @@
         </is>
       </c>
     </row>
-    <row r="2" s="5">
+    <row r="2" hidden="1" s="5">
       <c r="A2" s="4" t="inlineStr">
         <is>
           <t>2026-10-13 12:28:16</t>
@@ -1110,7 +1110,7 @@
         </is>
       </c>
     </row>
-    <row r="3" s="5">
+    <row r="3" hidden="1" s="5">
       <c r="A3" s="4" t="inlineStr">
         <is>
           <t>2026-10-13 12:29:07</t>
@@ -1149,7 +1149,7 @@
         </is>
       </c>
     </row>
-    <row r="4" s="5">
+    <row r="4" hidden="1" s="5">
       <c r="A4" s="4" t="inlineStr">
         <is>
           <t>2026-10-13 12:29:48</t>
@@ -1189,7 +1189,7 @@
         </is>
       </c>
     </row>
-    <row r="5" s="5">
+    <row r="5" hidden="1" s="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
           <t>2026-10-13 12:30:25</t>
@@ -1233,7 +1233,7 @@
         </is>
       </c>
     </row>
-    <row r="6" s="5">
+    <row r="6" hidden="1" s="5">
       <c r="A6" s="4" t="inlineStr">
         <is>
           <t>2026-10-13 12:31:06</t>
@@ -1279,7 +1279,7 @@
         </is>
       </c>
     </row>
-    <row r="7" s="5">
+    <row r="7" hidden="1" s="5">
       <c r="A7" s="4" t="inlineStr">
         <is>
           <t>2026-10-13 12:31:52</t>
@@ -1318,7 +1318,7 @@
         </is>
       </c>
     </row>
-    <row r="8" s="5">
+    <row r="8" hidden="1" s="5">
       <c r="A8" s="4" t="inlineStr">
         <is>
           <t>2026-10-13 12:32:21</t>
@@ -1357,7 +1357,7 @@
         </is>
       </c>
     </row>
-    <row r="9" s="5">
+    <row r="9" hidden="1" s="5">
       <c r="A9" s="4" t="inlineStr">
         <is>
           <t>2026-10-13 12:33:15</t>
@@ -1396,7 +1396,7 @@
         </is>
       </c>
     </row>
-    <row r="10" s="5">
+    <row r="10" hidden="1" s="5">
       <c r="A10" s="4" t="inlineStr">
         <is>
           <t>2026-10-13 12:33:41</t>
@@ -1435,7 +1435,7 @@
         </is>
       </c>
     </row>
-    <row r="11" s="5">
+    <row r="11" hidden="1" s="5">
       <c r="A11" s="4" t="inlineStr">
         <is>
           <t>2026-10-13 12:34:34</t>
@@ -1474,7 +1474,7 @@
         </is>
       </c>
     </row>
-    <row r="12" s="5">
+    <row r="12" hidden="1" s="5">
       <c r="A12" s="4" t="inlineStr">
         <is>
           <t>2026-10-13 12:35:07</t>
@@ -1513,7 +1513,7 @@
         </is>
       </c>
     </row>
-    <row r="13" s="5">
+    <row r="13" hidden="1" s="5">
       <c r="A13" s="4" t="inlineStr">
         <is>
           <t>2026-10-13 12:35:59</t>
@@ -1552,7 +1552,7 @@
         </is>
       </c>
     </row>
-    <row r="14" s="5">
+    <row r="14" hidden="1" s="5">
       <c r="A14" s="4" t="inlineStr">
         <is>
           <t>2026-10-13 12:36:29</t>
@@ -1591,7 +1591,7 @@
         </is>
       </c>
     </row>
-    <row r="15" s="5">
+    <row r="15" hidden="1" s="5">
       <c r="A15" s="4" t="inlineStr">
         <is>
           <t>2026-10-13 12:37:24</t>
@@ -1630,7 +1630,7 @@
         </is>
       </c>
     </row>
-    <row r="16" s="5">
+    <row r="16" hidden="1" s="5">
       <c r="A16" s="4" t="inlineStr">
         <is>
           <t>2026-10-13 12:37:50</t>
@@ -1669,7 +1669,7 @@
         </is>
       </c>
     </row>
-    <row r="17" s="5">
+    <row r="17" hidden="1" s="5">
       <c r="A17" s="4" t="inlineStr">
         <is>
           <t>2026-10-13 12:38:25</t>
@@ -1708,7 +1708,7 @@
         </is>
       </c>
     </row>
-    <row r="18" s="5">
+    <row r="18" hidden="1" s="5">
       <c r="A18" s="4" t="inlineStr">
         <is>
           <t>2026-10-13 12:39:32</t>
@@ -1747,7 +1747,7 @@
         </is>
       </c>
     </row>
-    <row r="19" s="5">
+    <row r="19" hidden="1" s="5">
       <c r="A19" s="4" t="inlineStr">
         <is>
           <t>2026-10-13 12:40:02</t>
@@ -1786,7 +1786,7 @@
         </is>
       </c>
     </row>
-    <row r="20" s="5">
+    <row r="20" hidden="1" s="5">
       <c r="A20" s="4" t="inlineStr">
         <is>
           <t>2026-10-13 12:40:53</t>
@@ -1825,7 +1825,7 @@
         </is>
       </c>
     </row>
-    <row r="21" s="5">
+    <row r="21" hidden="1" s="5">
       <c r="A21" s="4" t="inlineStr">
         <is>
           <t>2026-10-13 12:41:34</t>
@@ -1864,7 +1864,7 @@
         </is>
       </c>
     </row>
-    <row r="22" s="5">
+    <row r="22" hidden="1" s="5">
       <c r="A22" s="4" t="inlineStr">
         <is>
           <t>2026-10-13 12:42:03</t>
@@ -1903,7 +1903,7 @@
         </is>
       </c>
     </row>
-    <row r="23" s="5">
+    <row r="23" hidden="1" s="5">
       <c r="A23" s="4" t="inlineStr">
         <is>
           <t>2026-10-13 12:42:42</t>
@@ -1942,7 +1942,7 @@
         </is>
       </c>
     </row>
-    <row r="24" s="5">
+    <row r="24" hidden="1" s="5">
       <c r="A24" s="4" t="inlineStr">
         <is>
           <t>2026-10-13 12:43:27</t>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
     </row>
-    <row r="25" s="5">
+    <row r="25" hidden="1" s="5">
       <c r="A25" s="4" t="inlineStr">
         <is>
           <t>2026-10-13 12:44:15</t>
@@ -2025,7 +2025,7 @@
         </is>
       </c>
     </row>
-    <row r="26" s="5">
+    <row r="26" hidden="1" s="5">
       <c r="A26" s="4" t="inlineStr">
         <is>
           <t>2026-10-13 12:45:06</t>
@@ -2071,7 +2071,7 @@
         </is>
       </c>
     </row>
-    <row r="27" s="5">
+    <row r="27" hidden="1" s="5">
       <c r="A27" s="4" t="inlineStr">
         <is>
           <t>2026-10-13 12:45:49</t>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
     </row>
-    <row r="28" s="5">
+    <row r="28" hidden="1" s="5">
       <c r="A28" s="4" t="inlineStr">
         <is>
           <t>2026-10-13 12:46:32</t>
@@ -2156,7 +2156,7 @@
         </is>
       </c>
     </row>
-    <row r="29" s="5">
+    <row r="29" hidden="1" s="5">
       <c r="A29" s="4" t="inlineStr">
         <is>
           <t>2026-10-13 12:47:19</t>
@@ -2195,7 +2195,7 @@
         </is>
       </c>
     </row>
-    <row r="30" s="5">
+    <row r="30" hidden="1" s="5">
       <c r="A30" s="4" t="inlineStr">
         <is>
           <t>2026-10-13 12:48:14</t>
@@ -2234,7 +2234,7 @@
         </is>
       </c>
     </row>
-    <row r="31" s="5">
+    <row r="31" hidden="1" s="5">
       <c r="A31" s="4" t="inlineStr">
         <is>
           <t>2026-10-13 12:48:43</t>
@@ -2273,7 +2273,7 @@
         </is>
       </c>
     </row>
-    <row r="32" s="5">
+    <row r="32" hidden="1" s="5">
       <c r="A32" s="4" t="inlineStr">
         <is>
           <t>2026-10-13 12:49:11</t>
@@ -2312,7 +2312,7 @@
         </is>
       </c>
     </row>
-    <row r="33" s="5">
+    <row r="33" hidden="1" s="5">
       <c r="A33" s="4" t="inlineStr">
         <is>
           <t>2026-10-13 12:49:55</t>
@@ -2356,7 +2356,7 @@
         </is>
       </c>
     </row>
-    <row r="34" s="5">
+    <row r="34" hidden="1" s="5">
       <c r="A34" s="4" t="inlineStr">
         <is>
           <t>2026-10-13 12:50:50</t>
@@ -2396,7 +2396,7 @@
         </is>
       </c>
     </row>
-    <row r="35" s="5">
+    <row r="35" hidden="1" s="5">
       <c r="A35" s="4" t="inlineStr">
         <is>
           <t>2026-10-13 12:51:31</t>
@@ -2435,7 +2435,7 @@
         </is>
       </c>
     </row>
-    <row r="36" s="5">
+    <row r="36" hidden="1" s="5">
       <c r="A36" s="4" t="inlineStr">
         <is>
           <t>2026-10-13 12:51:57</t>
@@ -2474,7 +2474,7 @@
         </is>
       </c>
     </row>
-    <row r="37" s="5">
+    <row r="37" hidden="1" s="5">
       <c r="A37" s="4" t="inlineStr">
         <is>
           <t>2026-10-13 12:52:50</t>
@@ -2518,7 +2518,7 @@
         </is>
       </c>
     </row>
-    <row r="38" s="5">
+    <row r="38" hidden="1" s="5">
       <c r="A38" s="4" t="inlineStr">
         <is>
           <t>2026-10-13 12:53:48</t>
@@ -2562,7 +2562,7 @@
         </is>
       </c>
     </row>
-    <row r="39" s="5">
+    <row r="39" hidden="1" s="5">
       <c r="A39" s="4" t="inlineStr">
         <is>
           <t>2026-10-13 12:54:28</t>
@@ -2602,7 +2602,7 @@
         </is>
       </c>
     </row>
-    <row r="40" s="5">
+    <row r="40" hidden="1" s="5">
       <c r="A40" s="4" t="inlineStr">
         <is>
           <t>2026-10-13 12:55:22</t>
@@ -2641,7 +2641,7 @@
         </is>
       </c>
     </row>
-    <row r="41" s="5">
+    <row r="41" hidden="1" s="5">
       <c r="A41" s="4" t="inlineStr">
         <is>
           <t>2026-10-13 12:55:49</t>
@@ -2680,7 +2680,7 @@
         </is>
       </c>
     </row>
-    <row r="42" s="5">
+    <row r="42" hidden="1" s="5">
       <c r="A42" s="4" t="inlineStr">
         <is>
           <t>2026-10-13 12:56:26</t>
@@ -2720,7 +2720,7 @@
         </is>
       </c>
     </row>
-    <row r="43" s="5">
+    <row r="43" hidden="1" s="5">
       <c r="A43" s="4" t="inlineStr">
         <is>
           <t>2026-10-13 12:57:05</t>
@@ -2760,7 +2760,7 @@
         </is>
       </c>
     </row>
-    <row r="44" s="5">
+    <row r="44" hidden="1" s="5">
       <c r="A44" s="4" t="inlineStr">
         <is>
           <t>2026-10-13 12:57:53</t>
@@ -2800,7 +2800,7 @@
         </is>
       </c>
     </row>
-    <row r="45" s="5">
+    <row r="45" hidden="1" s="5">
       <c r="A45" s="4" t="inlineStr">
         <is>
           <t>2026-10-13 12:58:36</t>
@@ -2839,7 +2839,7 @@
         </is>
       </c>
     </row>
-    <row r="46" s="5">
+    <row r="46" hidden="1" s="5">
       <c r="A46" s="4" t="inlineStr">
         <is>
           <t>2026-10-13 12:59:16</t>
@@ -2879,7 +2879,7 @@
         </is>
       </c>
     </row>
-    <row r="47" s="5">
+    <row r="47" hidden="1" s="5">
       <c r="A47" s="4" t="inlineStr">
         <is>
           <t>2026-10-13 12:59:52</t>
@@ -2923,7 +2923,7 @@
         </is>
       </c>
     </row>
-    <row r="48" s="5">
+    <row r="48" hidden="1" s="5">
       <c r="A48" s="4" t="inlineStr">
         <is>
           <t>2026-10-13 13:00:42</t>
@@ -2967,7 +2967,7 @@
         </is>
       </c>
     </row>
-    <row r="49" s="5">
+    <row r="49" hidden="1" s="5">
       <c r="A49" s="4" t="inlineStr">
         <is>
           <t>2026-10-13 13:01:42</t>
@@ -3011,7 +3011,7 @@
         </is>
       </c>
     </row>
-    <row r="50" s="5">
+    <row r="50" hidden="1" s="5">
       <c r="A50" s="4" t="inlineStr">
         <is>
           <t>2026-10-13 13:02:39</t>
@@ -3055,7 +3055,7 @@
         </is>
       </c>
     </row>
-    <row r="51" s="5">
+    <row r="51" hidden="1" s="5">
       <c r="A51" s="4" t="inlineStr">
         <is>
           <t>2026-10-13 13:03:45</t>
@@ -3099,7 +3099,7 @@
         </is>
       </c>
     </row>
-    <row r="52" s="5">
+    <row r="52" hidden="1" s="5">
       <c r="A52" s="4" t="inlineStr">
         <is>
           <t>2026-10-13 13:04:39</t>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
     </row>
-    <row r="53" s="5">
+    <row r="53" hidden="1" s="5">
       <c r="A53" s="4" t="inlineStr">
         <is>
           <t>2026-10-13 13:05:31</t>
@@ -3187,7 +3187,7 @@
         </is>
       </c>
     </row>
-    <row r="54" s="5">
+    <row r="54" hidden="1" s="5">
       <c r="A54" s="4" t="inlineStr">
         <is>
           <t>2026-10-13 13:06:24</t>
@@ -3231,7 +3231,7 @@
         </is>
       </c>
     </row>
-    <row r="55" s="5">
+    <row r="55" hidden="1" s="5">
       <c r="A55" s="4" t="inlineStr">
         <is>
           <t>2026-10-13 13:07:20</t>
@@ -3275,7 +3275,7 @@
         </is>
       </c>
     </row>
-    <row r="56" s="5">
+    <row r="56" hidden="1" s="5">
       <c r="A56" s="4" t="inlineStr">
         <is>
           <t>2026-10-13 13:08:13</t>
@@ -3319,7 +3319,7 @@
         </is>
       </c>
     </row>
-    <row r="57" s="5">
+    <row r="57" hidden="1" s="5">
       <c r="A57" s="4" t="inlineStr">
         <is>
           <t>2026-10-13 13:09:15</t>
@@ -3363,7 +3363,7 @@
         </is>
       </c>
     </row>
-    <row r="58" s="5">
+    <row r="58" hidden="1" s="5">
       <c r="A58" s="4" t="inlineStr">
         <is>
           <t>2026-10-13 13:10:22</t>
@@ -3402,7 +3402,7 @@
         </is>
       </c>
     </row>
-    <row r="59" s="5">
+    <row r="59" hidden="1" s="5">
       <c r="A59" s="4" t="inlineStr">
         <is>
           <t>2026-10-13 13:11:12</t>
@@ -3446,7 +3446,7 @@
         </is>
       </c>
     </row>
-    <row r="60" s="5">
+    <row r="60" hidden="1" s="5">
       <c r="A60" s="4" t="inlineStr">
         <is>
           <t>2026-10-13 13:11:52</t>
@@ -3490,7 +3490,7 @@
         </is>
       </c>
     </row>
-    <row r="61" s="5">
+    <row r="61" hidden="1" s="5">
       <c r="A61" s="4" t="inlineStr">
         <is>
           <t>2026-10-13 13:12:42</t>
@@ -3534,7 +3534,7 @@
         </is>
       </c>
     </row>
-    <row r="62" s="5">
+    <row r="62" hidden="1" s="5">
       <c r="A62" s="4" t="inlineStr">
         <is>
           <t>2026-10-13 13:13:19</t>
@@ -3578,7 +3578,7 @@
         </is>
       </c>
     </row>
-    <row r="63" s="5">
+    <row r="63" hidden="1" s="5">
       <c r="A63" s="4" t="inlineStr">
         <is>
           <t>2026-10-13 13:14:10</t>
@@ -3622,7 +3622,7 @@
         </is>
       </c>
     </row>
-    <row r="64" s="5">
+    <row r="64" hidden="1" s="5">
       <c r="A64" s="4" t="inlineStr">
         <is>
           <t>2026-10-13 13:15:04</t>
@@ -3661,7 +3661,7 @@
         </is>
       </c>
     </row>
-    <row r="65" s="5">
+    <row r="65" hidden="1" s="5">
       <c r="A65" s="4" t="inlineStr">
         <is>
           <t>2026-10-13 13:15:38</t>
@@ -3705,7 +3705,7 @@
         </is>
       </c>
     </row>
-    <row r="66" s="5">
+    <row r="66" hidden="1" s="5">
       <c r="A66" s="4" t="inlineStr">
         <is>
           <t>2026-10-13 13:16:37</t>
@@ -3744,7 +3744,7 @@
         </is>
       </c>
     </row>
-    <row r="67" s="5">
+    <row r="67" hidden="1" s="5">
       <c r="A67" s="4" t="inlineStr">
         <is>
           <t>2026-10-13 13:17:35</t>
@@ -3783,7 +3783,7 @@
         </is>
       </c>
     </row>
-    <row r="68" s="5">
+    <row r="68" hidden="1" s="5">
       <c r="A68" s="4" t="inlineStr">
         <is>
           <t>2026-10-13 13:18:28</t>
@@ -3822,7 +3822,7 @@
         </is>
       </c>
     </row>
-    <row r="69" s="5">
+    <row r="69" hidden="1" s="5">
       <c r="A69" s="4" t="inlineStr">
         <is>
           <t>2026-10-13 13:19:08</t>
@@ -3866,7 +3866,7 @@
         </is>
       </c>
     </row>
-    <row r="70" s="5">
+    <row r="70" hidden="1" s="5">
       <c r="A70" s="4" t="inlineStr">
         <is>
           <t>2026-10-13 13:19:59</t>
@@ -3905,7 +3905,7 @@
         </is>
       </c>
     </row>
-    <row r="71" s="5">
+    <row r="71" hidden="1" s="5">
       <c r="A71" s="4" t="inlineStr">
         <is>
           <t>2026-10-13 13:20:56</t>
@@ -3944,7 +3944,7 @@
         </is>
       </c>
     </row>
-    <row r="72" s="5">
+    <row r="72" hidden="1" s="5">
       <c r="A72" s="4" t="inlineStr">
         <is>
           <t>2026-10-13 13:21:49</t>
@@ -3988,7 +3988,7 @@
         </is>
       </c>
     </row>
-    <row r="73" s="5">
+    <row r="73" hidden="1" s="5">
       <c r="A73" s="4" t="inlineStr">
         <is>
           <t>2026-10-13 13:22:40</t>
@@ -4032,7 +4032,7 @@
         </is>
       </c>
     </row>
-    <row r="74" s="5">
+    <row r="74" hidden="1" s="5">
       <c r="A74" s="4" t="inlineStr">
         <is>
           <t>2026-10-13 13:23:38</t>
@@ -4071,7 +4071,7 @@
         </is>
       </c>
     </row>
-    <row r="75" s="5">
+    <row r="75" hidden="1" s="5">
       <c r="A75" s="4" t="inlineStr">
         <is>
           <t>2026-10-13 13:24:33</t>
@@ -4110,7 +4110,7 @@
         </is>
       </c>
     </row>
-    <row r="76" s="5">
+    <row r="76" hidden="1" s="5">
       <c r="A76" s="4" t="inlineStr">
         <is>
           <t>2026-10-13 13:25:44</t>
@@ -4154,7 +4154,7 @@
         </is>
       </c>
     </row>
-    <row r="77" s="5">
+    <row r="77" hidden="1" s="5">
       <c r="A77" s="4" t="inlineStr">
         <is>
           <t>2026-10-13 13:26:33</t>
@@ -4198,7 +4198,7 @@
         </is>
       </c>
     </row>
-    <row r="78" s="5">
+    <row r="78" hidden="1" s="5">
       <c r="A78" s="4" t="inlineStr">
         <is>
           <t>2026-10-13 13:27:33</t>
@@ -4237,7 +4237,7 @@
         </is>
       </c>
     </row>
-    <row r="79" s="5">
+    <row r="79" hidden="1" s="5">
       <c r="A79" s="4" t="inlineStr">
         <is>
           <t>2026-10-13 13:28:31</t>
@@ -4281,7 +4281,7 @@
         </is>
       </c>
     </row>
-    <row r="80" s="5">
+    <row r="80" hidden="1" s="5">
       <c r="A80" s="4" t="inlineStr">
         <is>
           <t>2026-10-13 13:29:41</t>
@@ -4320,7 +4320,7 @@
         </is>
       </c>
     </row>
-    <row r="81" s="5">
+    <row r="81" hidden="1" s="5">
       <c r="A81" s="4" t="inlineStr">
         <is>
           <t>2026-10-13 13:30:38</t>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
     </row>
-    <row r="82" s="5">
+    <row r="82" hidden="1" s="5">
       <c r="A82" s="4" t="inlineStr">
         <is>
           <t>2026-10-13 13:31:08</t>
@@ -4394,7 +4394,7 @@
         </is>
       </c>
     </row>
-    <row r="83" s="5">
+    <row r="83" hidden="1" s="5">
       <c r="A83" s="4" t="inlineStr">
         <is>
           <t>2026-10-13 13:32:02</t>
@@ -4429,7 +4429,7 @@
         </is>
       </c>
     </row>
-    <row r="84" s="5">
+    <row r="84" hidden="1" s="5">
       <c r="A84" s="4" t="inlineStr">
         <is>
           <t>2026-10-13 13:32:55</t>
@@ -4464,7 +4464,7 @@
         </is>
       </c>
     </row>
-    <row r="85" s="5">
+    <row r="85" hidden="1" s="5">
       <c r="A85" s="4" t="inlineStr">
         <is>
           <t>2026-10-13 13:34:22</t>
@@ -4506,7 +4506,7 @@
         </is>
       </c>
     </row>
-    <row r="86" s="5">
+    <row r="86" hidden="1" s="5">
       <c r="A86" s="4" t="inlineStr">
         <is>
           <t>2026-10-13 13:35:23</t>
@@ -4541,7 +4541,7 @@
         </is>
       </c>
     </row>
-    <row r="87" s="5">
+    <row r="87" hidden="1" s="5">
       <c r="A87" s="4" t="inlineStr">
         <is>
           <t>2026-10-13 13:36:08</t>
@@ -4576,7 +4576,7 @@
         </is>
       </c>
     </row>
-    <row r="88" s="5">
+    <row r="88" hidden="1" s="5">
       <c r="A88" s="4" t="inlineStr">
         <is>
           <t>2026-10-13 13:36:48</t>
@@ -4616,7 +4616,7 @@
         </is>
       </c>
     </row>
-    <row r="89" s="5">
+    <row r="89" hidden="1" s="5">
       <c r="A89" s="4" t="inlineStr">
         <is>
           <t>2026-10-13 13:37:41</t>
@@ -4652,7 +4652,7 @@
         </is>
       </c>
     </row>
-    <row r="90" s="5">
+    <row r="90" hidden="1" s="5">
       <c r="A90" s="4" t="inlineStr">
         <is>
           <t>2026-10-13 13:38:37</t>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
     </row>
-    <row r="91" s="5">
+    <row r="91" hidden="1" s="5">
       <c r="A91" s="4" t="inlineStr">
         <is>
           <t>2026-10-13 13:39:08</t>
@@ -4722,7 +4722,7 @@
         </is>
       </c>
     </row>
-    <row r="92" s="5">
+    <row r="92" hidden="1" s="5">
       <c r="A92" s="4" t="inlineStr">
         <is>
           <t>2026-10-13 13:39:57</t>
@@ -4764,7 +4764,7 @@
         </is>
       </c>
     </row>
-    <row r="93" s="5">
+    <row r="93" hidden="1" s="5">
       <c r="A93" s="4" t="inlineStr">
         <is>
           <t>2026-10-13 13:40:47</t>
@@ -4804,7 +4804,7 @@
         </is>
       </c>
     </row>
-    <row r="94" s="5">
+    <row r="94" hidden="1" s="5">
       <c r="A94" s="4" t="inlineStr">
         <is>
           <t>2026-10-13 13:41:31</t>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
     </row>
-    <row r="95" s="5">
+    <row r="95" hidden="1" s="5">
       <c r="A95" s="4" t="inlineStr">
         <is>
           <t>2026-10-13 13:42:07</t>
@@ -4874,7 +4874,7 @@
         </is>
       </c>
     </row>
-    <row r="96" s="5">
+    <row r="96" hidden="1" s="5">
       <c r="A96" s="4" t="inlineStr">
         <is>
           <t>2026-10-13 13:42:48</t>
@@ -4909,7 +4909,7 @@
         </is>
       </c>
     </row>
-    <row r="97" s="5">
+    <row r="97" hidden="1" s="5">
       <c r="A97" s="4" t="inlineStr">
         <is>
           <t>2026-10-13 13:43:28</t>
@@ -4944,7 +4944,7 @@
         </is>
       </c>
     </row>
-    <row r="98" s="5">
+    <row r="98" hidden="1" s="5">
       <c r="A98" s="4" t="inlineStr">
         <is>
           <t>2026-10-13 13:44:23</t>
@@ -4980,7 +4980,7 @@
         </is>
       </c>
     </row>
-    <row r="99" s="5">
+    <row r="99" hidden="1" s="5">
       <c r="A99" s="4" t="inlineStr">
         <is>
           <t>2026-10-13 13:45:13</t>
@@ -5020,7 +5020,7 @@
         </is>
       </c>
     </row>
-    <row r="100" s="5">
+    <row r="100" hidden="1" s="5">
       <c r="A100" s="4" t="inlineStr">
         <is>
           <t>2026-10-13 13:45:54</t>
@@ -5055,7 +5055,7 @@
         </is>
       </c>
     </row>
-    <row r="101" s="5">
+    <row r="101" hidden="1" s="5">
       <c r="A101" s="4" t="inlineStr">
         <is>
           <t>2026-10-13 13:46:37</t>
@@ -5090,7 +5090,7 @@
         </is>
       </c>
     </row>
-    <row r="102" s="5">
+    <row r="102" hidden="1" s="5">
       <c r="A102" s="4" t="inlineStr">
         <is>
           <t>2026-10-13 13:47:24</t>
@@ -5130,7 +5130,7 @@
         </is>
       </c>
     </row>
-    <row r="103" s="5">
+    <row r="103" hidden="1" s="5">
       <c r="A103" s="4" t="inlineStr">
         <is>
           <t>2026-10-13 13:48:13</t>
@@ -5172,7 +5172,7 @@
         </is>
       </c>
     </row>
-    <row r="104" s="5">
+    <row r="104" hidden="1" s="5">
       <c r="A104" s="4" t="inlineStr">
         <is>
           <t>2026-10-13 13:48:38</t>
@@ -5226,7 +5226,7 @@
         </is>
       </c>
     </row>
-    <row r="105" s="5">
+    <row r="105" hidden="1" s="5">
       <c r="A105" s="4" t="inlineStr">
         <is>
           <t>2026-10-13 13:49:41</t>
